--- a/AdditionalUniqueNPC/package/LangMod/JP/Dialog/dialog.xlsx
+++ b/AdditionalUniqueNPC/package/LangMod/JP/Dialog/dialog.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -39,6 +39,12 @@
 お砂糖、スパイス、そして素敵な闇いっぱい。そんなものでお嬢様はできているんだ。
 ひとつ助言してやろう。悪魔の角はうかつに撫でないことだ。わたしの機嫌が悪くなるからな。ああ、だからそれを下ろせと言っている。
 この本か？ これはわたしの日記だ。旅の経験や気になった出来事を絵で残しているんだ。見てみるか？ …ん？ この化け物はなにかって？ 失礼な！これはわたしが丹精込めて描いた雪プチだぞ！ おい、日記を返せ！</t>
+  </si>
+  <si>
+    <t>mc_aun_eirwen</t>
+  </si>
+  <si>
+    <t>私ね、「見た目の印象と違う」ってよく言われるんだ。別に取り繕っているつもりはないんだけど…。</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -438,6 +444,14 @@
       </c>
       <c r="C5" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
